--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2875C1FA-E973-40DF-991E-C0F61F5B26D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DEAE06-0E79-426C-B7B6-16472EBEF166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1515" yWindow="0" windowWidth="11640" windowHeight="10800" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="67">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -234,6 +234,9 @@
   </si>
   <si>
     <t>12/01 - 19/01</t>
+  </si>
+  <si>
+    <t>finish</t>
   </si>
 </sst>
 </file>
@@ -714,6 +717,9 @@
       <c r="D3" t="s">
         <v>51</v>
       </c>
+      <c r="E3" t="s">
+        <v>66</v>
+      </c>
       <c r="H3" t="s">
         <v>46</v>
       </c>
@@ -731,6 +737,9 @@
       <c r="D4" t="s">
         <v>51</v>
       </c>
+      <c r="E4" t="s">
+        <v>66</v>
+      </c>
       <c r="H4" t="s">
         <v>47</v>
       </c>
@@ -780,6 +789,9 @@
       <c r="D7" t="s">
         <v>54</v>
       </c>
+      <c r="E7" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
@@ -891,8 +903,11 @@
       <c r="D16" s="4" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="17" spans="1:4">
+      <c r="E16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
         <v>16</v>
       </c>
@@ -903,7 +918,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
         <v>17</v>
       </c>
@@ -911,7 +926,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
         <v>18</v>
       </c>
@@ -922,7 +937,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
         <v>19</v>
       </c>
@@ -933,7 +948,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:4" ht="14.25">
+    <row r="21" spans="1:5" ht="14.25">
       <c r="A21" s="2" t="s">
         <v>21</v>
       </c>
@@ -944,7 +959,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="14.25">
+    <row r="22" spans="1:5" ht="14.25">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
@@ -955,7 +970,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="1:4" ht="14.25">
+    <row r="23" spans="1:5" ht="14.25">
       <c r="A23" s="2" t="s">
         <v>23</v>
       </c>
@@ -966,7 +981,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="24" spans="1:4" ht="14.25">
+    <row r="24" spans="1:5" ht="14.25">
       <c r="A24" s="2" t="s">
         <v>24</v>
       </c>
@@ -977,7 +992,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:4" ht="14.25">
+    <row r="25" spans="1:5" ht="14.25">
       <c r="A25" s="2" t="s">
         <v>25</v>
       </c>
@@ -988,7 +1003,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="26" spans="1:4" ht="14.25">
+    <row r="26" spans="1:5" ht="14.25">
       <c r="A26" s="2" t="s">
         <v>26</v>
       </c>
@@ -999,7 +1014,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="27" spans="1:4" ht="14.25">
+    <row r="27" spans="1:5" ht="14.25">
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
@@ -1010,7 +1025,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="28" spans="1:4" ht="14.25">
+    <row r="28" spans="1:5" ht="14.25">
       <c r="A28" s="2" t="s">
         <v>28</v>
       </c>
@@ -1021,7 +1036,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="29" spans="1:4" ht="14.25">
+    <row r="29" spans="1:5" ht="14.25">
       <c r="A29" s="2" t="s">
         <v>29</v>
       </c>
@@ -1032,7 +1047,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="30" spans="1:4" ht="14.25">
+    <row r="30" spans="1:5" ht="14.25">
       <c r="A30" s="2" t="s">
         <v>30</v>
       </c>
@@ -1043,7 +1058,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="31" spans="1:4" ht="14.25">
+    <row r="31" spans="1:5" ht="14.25">
       <c r="A31" s="2" t="s">
         <v>31</v>
       </c>
@@ -1053,8 +1068,11 @@
       <c r="D31" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="32" spans="1:4" ht="14.25">
+      <c r="E31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="14.25">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -1064,8 +1082,11 @@
       <c r="D32" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="33" spans="1:4" ht="14.25">
+      <c r="E32" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="14.25">
       <c r="A33" s="2" t="s">
         <v>33</v>
       </c>
@@ -1075,8 +1096,11 @@
       <c r="D33" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="34" spans="1:4" ht="14.25">
+      <c r="E33" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="14.25">
       <c r="A34" s="5" t="s">
         <v>34</v>
       </c>
@@ -1087,7 +1111,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="35" spans="1:4" ht="14.25">
+    <row r="35" spans="1:5" ht="14.25">
       <c r="A35" s="2" t="s">
         <v>35</v>
       </c>
@@ -1098,7 +1122,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="36" spans="1:4" ht="14.25">
+    <row r="36" spans="1:5" ht="14.25">
       <c r="A36" s="5" t="s">
         <v>36</v>
       </c>
@@ -1109,7 +1133,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="37" spans="1:4" ht="14.25">
+    <row r="37" spans="1:5" ht="14.25">
       <c r="A37" s="2" t="s">
         <v>37</v>
       </c>
@@ -1120,7 +1144,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="38" spans="1:4" ht="14.25">
+    <row r="38" spans="1:5" ht="14.25">
       <c r="A38" s="2" t="s">
         <v>38</v>
       </c>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{32DEAE06-0E79-426C-B7B6-16472EBEF166}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AADA28-1420-47AA-8E58-133886C564BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -47,60 +47,9 @@
     <t>deadline</t>
   </si>
   <si>
-    <t>biriscv_alu</t>
-  </si>
-  <si>
-    <t>biriscv_csr</t>
-  </si>
-  <si>
-    <t>biriscv_decode</t>
-  </si>
-  <si>
-    <t>biriscv_decoder</t>
-  </si>
-  <si>
-    <t>biriscv_defs</t>
-  </si>
-  <si>
-    <t>biriscv_exec</t>
-  </si>
-  <si>
-    <t>biriscv_fetch</t>
-  </si>
-  <si>
-    <t>biriscv_frontend</t>
-  </si>
-  <si>
-    <t>biriscv_issue</t>
-  </si>
-  <si>
-    <t>biriscv_lsu</t>
-  </si>
-  <si>
-    <t>biriscv_mmu</t>
-  </si>
-  <si>
-    <t>biriscv_npc</t>
-  </si>
-  <si>
-    <t>biriscv_pipe_ctrl</t>
-  </si>
-  <si>
-    <t>biriscv_regfile</t>
-  </si>
-  <si>
-    <t>biriscv_trace_sim</t>
-  </si>
-  <si>
-    <t>biriscv_xilinx_2r1w</t>
-  </si>
-  <si>
     <t>dcache</t>
   </si>
   <si>
-    <t xml:space="preserve">biriscv_csr_regfile </t>
-  </si>
-  <si>
     <t>dcache_axi</t>
   </si>
   <si>
@@ -173,9 +122,6 @@
     <t>yzn</t>
   </si>
   <si>
-    <t>biriscv_divider+mul</t>
-  </si>
-  <si>
     <t>03/01 - 19/01</t>
   </si>
   <si>
@@ -237,6 +183,60 @@
   </si>
   <si>
     <t>finish</t>
+  </si>
+  <si>
+    <t>riscv_alu</t>
+  </si>
+  <si>
+    <t>riscv_csr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">riscv_csr_regfile </t>
+  </si>
+  <si>
+    <t>riscv_decode</t>
+  </si>
+  <si>
+    <t>riscv_decoder</t>
+  </si>
+  <si>
+    <t>riscv_defs</t>
+  </si>
+  <si>
+    <t>riscv_divider+mul</t>
+  </si>
+  <si>
+    <t>riscv_exec</t>
+  </si>
+  <si>
+    <t>riscv_fetch</t>
+  </si>
+  <si>
+    <t>riscv_frontend</t>
+  </si>
+  <si>
+    <t>riscv_issue</t>
+  </si>
+  <si>
+    <t>riscv_lsu</t>
+  </si>
+  <si>
+    <t>riscv_mmu</t>
+  </si>
+  <si>
+    <t>riscv_npc</t>
+  </si>
+  <si>
+    <t>riscv_pipe_ctrl</t>
+  </si>
+  <si>
+    <t>riscv_regfile</t>
+  </si>
+  <si>
+    <t>riscv_trace_sim</t>
+  </si>
+  <si>
+    <t>riscv_xilinx_2r1w</t>
   </si>
 </sst>
 </file>
@@ -675,484 +675,484 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>39</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="1" t="s">
-        <v>3</v>
+        <v>49</v>
       </c>
       <c r="B2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E2" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="I2" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="B3" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E3" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
       <c r="I3" t="s">
-        <v>46</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="B4" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
       <c r="E4" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
       <c r="H4" t="s">
-        <v>47</v>
+        <v>29</v>
       </c>
       <c r="I4" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="1" t="s">
-        <v>5</v>
+        <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
       <c r="E5" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F5" s="6"/>
       <c r="I5" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="1" t="s">
-        <v>6</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>53</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="1" t="s">
-        <v>7</v>
+        <v>54</v>
       </c>
       <c r="B7" t="s">
-        <v>55</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="1" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B8" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="E8" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
-        <v>9</v>
+        <v>57</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="3" t="s">
-        <v>10</v>
+        <v>58</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>59</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D12" t="s">
-        <v>57</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>12</v>
+        <v>60</v>
       </c>
       <c r="B13" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>56</v>
+        <v>38</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>13</v>
+        <v>61</v>
       </c>
       <c r="B14" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>14</v>
+        <v>62</v>
       </c>
       <c r="B15" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="F15" s="6"/>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>15</v>
+        <v>63</v>
       </c>
       <c r="B16" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="E16" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
-        <v>16</v>
+        <v>64</v>
       </c>
       <c r="B17" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D17" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>17</v>
+        <v>65</v>
       </c>
       <c r="B18" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="1" t="s">
-        <v>18</v>
+        <v>66</v>
       </c>
       <c r="B19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D19" t="s">
         <v>44</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s">
         <v>44</v>
-      </c>
-      <c r="D20" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="14.25">
       <c r="A21" s="2" t="s">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="B21" t="s">
+        <v>27</v>
+      </c>
+      <c r="D21" t="s">
         <v>44</v>
-      </c>
-      <c r="D21" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.25">
       <c r="A22" s="2" t="s">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25">
       <c r="A23" s="2" t="s">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D23" t="s">
-        <v>48</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25">
       <c r="A24" s="2" t="s">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="B24" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25">
       <c r="A25" s="2" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.25">
       <c r="A26" s="2" t="s">
-        <v>26</v>
+        <v>9</v>
       </c>
       <c r="B26" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D26" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25">
       <c r="A27" s="2" t="s">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D27" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25">
       <c r="A28" s="2" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B28" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D28" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25">
       <c r="A29" s="2" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B29" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D29" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="14.25">
       <c r="A30" s="2" t="s">
-        <v>30</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D30" t="s">
-        <v>63</v>
+        <v>45</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25">
       <c r="A31" s="2" t="s">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E31" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25">
       <c r="A32" s="2" t="s">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E32" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25">
       <c r="A33" s="2" t="s">
-        <v>33</v>
+        <v>16</v>
       </c>
       <c r="B33" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
       <c r="E33" t="s">
-        <v>66</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25">
       <c r="A34" s="5" t="s">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="B34" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25">
       <c r="A35" s="2" t="s">
-        <v>35</v>
+        <v>18</v>
       </c>
       <c r="B35" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25">
       <c r="A36" s="5" t="s">
-        <v>36</v>
+        <v>19</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.25">
       <c r="A37" s="2" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B37" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="14.25">
       <c r="A38" s="2" t="s">
-        <v>38</v>
+        <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03AADA28-1420-47AA-8E58-133886C564BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0DE7C4-1B8D-4649-B563-FE3B149EA439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="68">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -203,9 +203,6 @@
     <t>riscv_defs</t>
   </si>
   <si>
-    <t>riscv_divider+mul</t>
-  </si>
-  <si>
     <t>riscv_exec</t>
   </si>
   <si>
@@ -237,6 +234,12 @@
   </si>
   <si>
     <t>riscv_xilinx_2r1w</t>
+  </si>
+  <si>
+    <t>riscv_multipier</t>
+  </si>
+  <si>
+    <t>riscv_divider</t>
   </si>
 </sst>
 </file>
@@ -283,7 +286,7 @@
       <charset val="177"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -302,6 +305,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -315,7 +324,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -323,6 +332,8 @@
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -657,7 +668,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9373D2A7-8D80-423E-9070-95B67CA8F36B}">
-  <dimension ref="A1:I38"/>
+  <dimension ref="A1:I39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.375" style="1" customWidth="1"/>
@@ -685,7 +696,7 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="7" t="s">
         <v>49</v>
       </c>
       <c r="B2" t="s">
@@ -708,7 +719,7 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="1" t="s">
+      <c r="A3" s="7" t="s">
         <v>50</v>
       </c>
       <c r="B3" t="s">
@@ -728,7 +739,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="1" t="s">
+      <c r="A4" s="7" t="s">
         <v>51</v>
       </c>
       <c r="B4" t="s">
@@ -748,7 +759,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="1" t="s">
+      <c r="A5" s="7" t="s">
         <v>52</v>
       </c>
       <c r="B5" t="s">
@@ -769,7 +780,7 @@
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="1" t="s">
+      <c r="A6" s="7" t="s">
         <v>53</v>
       </c>
       <c r="B6" t="s">
@@ -778,9 +789,12 @@
       <c r="D6" t="s">
         <v>35</v>
       </c>
+      <c r="E6" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="1" t="s">
+      <c r="A7" s="7" t="s">
         <v>54</v>
       </c>
       <c r="B7" t="s">
@@ -794,8 +808,8 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="1" t="s">
-        <v>55</v>
+      <c r="A8" s="7" t="s">
+        <v>66</v>
       </c>
       <c r="B8" t="s">
         <v>24</v>
@@ -803,143 +817,143 @@
       <c r="C8" t="s">
         <v>25</v>
       </c>
-      <c r="D8" t="s">
-        <v>32</v>
-      </c>
       <c r="E8" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="1" t="s">
-        <v>56</v>
+      <c r="A9" s="7" t="s">
+        <v>67</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" t="s">
-        <v>40</v>
+        <v>24</v>
+      </c>
+      <c r="C9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>27</v>
+      </c>
+      <c r="D10" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" t="s">
+        <v>25</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="B10" t="s">
-        <v>24</v>
-      </c>
-      <c r="C10" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F10" s="6"/>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="D11" t="s">
+      <c r="B12" t="s">
+        <v>24</v>
+      </c>
+      <c r="D12" t="s">
         <v>38</v>
       </c>
-      <c r="F11" s="6"/>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D12" t="s">
-        <v>39</v>
-      </c>
+      <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B13" t="s">
         <v>27</v>
       </c>
       <c r="D13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B14" t="s">
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B15" t="s">
         <v>27</v>
       </c>
-      <c r="D15" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="F15" s="6"/>
+      <c r="D15" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="E16" t="s">
-        <v>48</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B18" t="s">
+        <v>27</v>
+      </c>
+      <c r="D18" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B17" t="s">
-        <v>27</v>
-      </c>
-      <c r="D17" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B18" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="1" t="s">
-        <v>66</v>
-      </c>
       <c r="B19" t="s">
-        <v>27</v>
-      </c>
-      <c r="D19" t="s">
-        <v>44</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="1" t="s">
-        <v>3</v>
+        <v>65</v>
       </c>
       <c r="B20" t="s">
         <v>27</v>
@@ -948,9 +962,9 @@
         <v>44</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="14.25">
-      <c r="A21" s="2" t="s">
-        <v>4</v>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="B21" t="s">
         <v>27</v>
@@ -961,18 +975,18 @@
     </row>
     <row r="22" spans="1:5" ht="14.25">
       <c r="A22" s="2" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
       </c>
       <c r="D22" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25">
       <c r="A23" s="2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B23" t="s">
         <v>27</v>
@@ -983,18 +997,18 @@
     </row>
     <row r="24" spans="1:5" ht="14.25">
       <c r="A24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B24" t="s">
         <v>27</v>
       </c>
       <c r="D24" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25">
       <c r="A25" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
@@ -1005,7 +1019,7 @@
     </row>
     <row r="26" spans="1:5" ht="14.25">
       <c r="A26" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
@@ -1016,7 +1030,7 @@
     </row>
     <row r="27" spans="1:5" ht="14.25">
       <c r="A27" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
@@ -1027,7 +1041,7 @@
     </row>
     <row r="28" spans="1:5" ht="14.25">
       <c r="A28" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" t="s">
         <v>27</v>
@@ -1038,7 +1052,7 @@
     </row>
     <row r="29" spans="1:5" ht="14.25">
       <c r="A29" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B29" t="s">
         <v>27</v>
@@ -1049,7 +1063,7 @@
     </row>
     <row r="30" spans="1:5" ht="14.25">
       <c r="A30" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B30" t="s">
         <v>27</v>
@@ -1060,21 +1074,18 @@
     </row>
     <row r="31" spans="1:5" ht="14.25">
       <c r="A31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" t="s">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" ht="14.25">
+      <c r="A32" s="8" t="s">
         <v>14</v>
-      </c>
-      <c r="B31" t="s">
-        <v>24</v>
-      </c>
-      <c r="D31" t="s">
-        <v>47</v>
-      </c>
-      <c r="E31" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" ht="14.25">
-      <c r="A32" s="2" t="s">
-        <v>15</v>
       </c>
       <c r="B32" t="s">
         <v>24</v>
@@ -1087,8 +1098,8 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25">
-      <c r="A33" s="2" t="s">
-        <v>16</v>
+      <c r="A33" s="8" t="s">
+        <v>15</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -1101,44 +1112,47 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B34" t="s">
+        <v>24</v>
+      </c>
+      <c r="D34" t="s">
+        <v>47</v>
+      </c>
+      <c r="E34" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" ht="14.25">
+      <c r="A35" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B34" t="s">
-        <v>27</v>
-      </c>
-      <c r="D34" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" ht="14.25">
-      <c r="A35" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D35" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25">
-      <c r="A36" s="5" t="s">
-        <v>19</v>
+      <c r="A36" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B36" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.25">
-      <c r="A37" s="2" t="s">
-        <v>20</v>
+      <c r="A37" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D37" t="s">
         <v>46</v>
@@ -1146,12 +1160,23 @@
     </row>
     <row r="38" spans="1:5" ht="14.25">
       <c r="A38" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B38" t="s">
+        <v>24</v>
+      </c>
+      <c r="D38" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" ht="14.25">
+      <c r="A39" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B38" t="s">
-        <v>24</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" t="s">
         <v>46</v>
       </c>
     </row>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B0DE7C4-1B8D-4649-B563-FE3B149EA439}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5C0651-0745-484B-ABFF-CE6D0C6FEA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="68">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -885,7 +885,7 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="7" t="s">
         <v>59</v>
       </c>
       <c r="B14" t="s">
@@ -894,9 +894,12 @@
       <c r="D14" t="s">
         <v>38</v>
       </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="7" t="s">
         <v>60</v>
       </c>
       <c r="B15" t="s">
@@ -904,6 +907,9 @@
       </c>
       <c r="D15" t="s">
         <v>41</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -919,11 +925,11 @@
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="1" t="s">
+      <c r="A17" s="7" t="s">
         <v>62</v>
       </c>
       <c r="B17" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>43</v>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB5C0651-0745-484B-ABFF-CE6D0C6FEA36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A3E642-E238-46AB-A114-9578D730E985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="68">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -980,7 +980,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" s="8" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
@@ -988,6 +988,9 @@
       </c>
       <c r="D22" t="s">
         <v>44</v>
+      </c>
+      <c r="E22" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25">

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5A3E642-E238-46AB-A114-9578D730E985}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1FF9ED-347A-446A-8202-7C643647C5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -240,6 +240,9 @@
   </si>
   <si>
     <t>riscv_divider</t>
+  </si>
+  <si>
+    <t>dcache_axi_fifo</t>
   </si>
 </sst>
 </file>
@@ -668,7 +671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9373D2A7-8D80-423E-9070-95B67CA8F36B}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.375" style="1" customWidth="1"/>
@@ -984,7 +987,7 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D22" t="s">
         <v>44</v>
@@ -994,41 +997,47 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B23" t="s">
+        <v>24</v>
+      </c>
+      <c r="D23" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" ht="14.25">
+      <c r="A24" s="8" t="s">
         <v>5</v>
       </c>
-      <c r="B23" t="s">
-        <v>27</v>
-      </c>
-      <c r="D23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" ht="14.25">
-      <c r="A24" s="2" t="s">
-        <v>6</v>
-      </c>
       <c r="B24" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D24" t="s">
-        <v>30</v>
+        <v>44</v>
+      </c>
+      <c r="E24" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25">
       <c r="A25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B25" t="s">
         <v>27</v>
       </c>
       <c r="D25" t="s">
-        <v>45</v>
+        <v>30</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.25">
       <c r="A26" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
         <v>27</v>
@@ -1039,7 +1048,7 @@
     </row>
     <row r="27" spans="1:5" ht="14.25">
       <c r="A27" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B27" t="s">
         <v>27</v>
@@ -1050,7 +1059,7 @@
     </row>
     <row r="28" spans="1:5" ht="14.25">
       <c r="A28" s="2" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B28" t="s">
         <v>27</v>
@@ -1061,7 +1070,7 @@
     </row>
     <row r="29" spans="1:5" ht="14.25">
       <c r="A29" s="2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" t="s">
         <v>27</v>
@@ -1072,7 +1081,7 @@
     </row>
     <row r="30" spans="1:5" ht="14.25">
       <c r="A30" s="2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30" t="s">
         <v>27</v>
@@ -1083,7 +1092,7 @@
     </row>
     <row r="31" spans="1:5" ht="14.25">
       <c r="A31" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B31" t="s">
         <v>27</v>
@@ -1093,22 +1102,19 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25">
-      <c r="A32" s="8" t="s">
-        <v>14</v>
+      <c r="A32" s="2" t="s">
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D32" t="s">
-        <v>47</v>
-      </c>
-      <c r="E32" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25">
       <c r="A33" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
@@ -1122,7 +1128,7 @@
     </row>
     <row r="34" spans="1:5" ht="14.25">
       <c r="A34" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -1135,44 +1141,47 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>24</v>
+      </c>
+      <c r="D35" t="s">
+        <v>47</v>
+      </c>
+      <c r="E35" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="14.25">
+      <c r="A36" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B35" t="s">
-        <v>27</v>
-      </c>
-      <c r="D35" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" ht="14.25">
-      <c r="A36" s="2" t="s">
-        <v>18</v>
-      </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D36" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.25">
-      <c r="A37" s="5" t="s">
-        <v>19</v>
+      <c r="A37" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B37" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D37" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="14.25">
-      <c r="A38" s="2" t="s">
-        <v>20</v>
+      <c r="A38" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
@@ -1180,12 +1189,23 @@
     </row>
     <row r="39" spans="1:5" ht="14.25">
       <c r="A39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="D39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="14.25">
+      <c r="A40" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B39" t="s">
-        <v>24</v>
-      </c>
-      <c r="D39" t="s">
+      <c r="B40" t="s">
+        <v>24</v>
+      </c>
+      <c r="D40" t="s">
         <v>46</v>
       </c>
     </row>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF1FF9ED-347A-446A-8202-7C643647C5AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE5C5DA-FED1-4F30-8F6A-79139C115554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="70">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -243,6 +243,9 @@
   </si>
   <si>
     <t>dcache_axi_fifo</t>
+  </si>
+  <si>
+    <t>tcm_mem_ram</t>
   </si>
 </sst>
 </file>
@@ -671,7 +674,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9373D2A7-8D80-423E-9070-95B67CA8F36B}">
-  <dimension ref="A1:I40"/>
+  <dimension ref="A1:I41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.375" style="1" customWidth="1"/>
@@ -1209,6 +1212,20 @@
         <v>46</v>
       </c>
     </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="7" t="s">
+        <v>69</v>
+      </c>
+      <c r="B41" t="s">
+        <v>24</v>
+      </c>
+      <c r="D41" t="s">
+        <v>46</v>
+      </c>
+      <c r="E41" t="s">
+        <v>48</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EE5C5DA-FED1-4F30-8F6A-79139C115554}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F40C13-3569-4B41-A98E-9397D4FCD0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -246,13 +246,16 @@
   </si>
   <si>
     <t>tcm_mem_ram</t>
+  </si>
+  <si>
+    <t>dport_axi_fifo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -290,6 +293,12 @@
       <color rgb="FFFF0000"/>
       <name val="Arial Unicode MS"/>
       <charset val="177"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="5">
@@ -330,7 +339,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -340,6 +349,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -674,7 +685,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9373D2A7-8D80-423E-9070-95B67CA8F36B}">
-  <dimension ref="A1:I41"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="19.375" style="1" customWidth="1"/>
@@ -842,7 +853,7 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="7" t="s">
         <v>55</v>
       </c>
       <c r="B10" t="s">
@@ -850,6 +861,9 @@
       </c>
       <c r="D10" t="s">
         <v>40</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -868,7 +882,7 @@
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="7" t="s">
         <v>57</v>
       </c>
       <c r="B12" t="s">
@@ -877,10 +891,13 @@
       <c r="D12" t="s">
         <v>38</v>
       </c>
+      <c r="E12" t="s">
+        <v>48</v>
+      </c>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="7" t="s">
         <v>58</v>
       </c>
       <c r="B13" t="s">
@@ -888,6 +905,9 @@
       </c>
       <c r="D13" t="s">
         <v>39</v>
+      </c>
+      <c r="E13" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -945,14 +965,17 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="1" t="s">
+      <c r="A18" s="7" t="s">
         <v>63</v>
       </c>
       <c r="B18" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D18" t="s">
         <v>42</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -964,14 +987,17 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="1" t="s">
+      <c r="A20" s="7" t="s">
         <v>65</v>
       </c>
       <c r="B20" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D20" t="s">
         <v>44</v>
+      </c>
+      <c r="E20" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1094,36 +1120,42 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" s="8" t="s">
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D31" t="s">
         <v>45</v>
       </c>
+      <c r="E31" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="32" spans="1:5" ht="14.25">
-      <c r="A32" s="2" t="s">
-        <v>13</v>
+      <c r="A32" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="B32" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D32" t="s">
         <v>45</v>
       </c>
+      <c r="E32" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="33" spans="1:5" ht="14.25">
       <c r="A33" s="8" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
         <v>24</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E33" t="s">
         <v>48</v>
@@ -1131,7 +1163,7 @@
     </row>
     <row r="34" spans="1:5" ht="14.25">
       <c r="A34" s="8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B34" t="s">
         <v>24</v>
@@ -1145,7 +1177,7 @@
     </row>
     <row r="35" spans="1:5" ht="14.25">
       <c r="A35" s="8" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B35" t="s">
         <v>24</v>
@@ -1158,19 +1190,22 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="D36" t="s">
+        <v>47</v>
+      </c>
+      <c r="E36" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" ht="14.25">
+      <c r="A37" s="10" t="s">
         <v>17</v>
-      </c>
-      <c r="B36" t="s">
-        <v>27</v>
-      </c>
-      <c r="D36" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" ht="14.25">
-      <c r="A37" s="2" t="s">
-        <v>18</v>
       </c>
       <c r="B37" t="s">
         <v>24</v>
@@ -1178,32 +1213,35 @@
       <c r="D37" t="s">
         <v>46</v>
       </c>
+      <c r="E37" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="38" spans="1:5" ht="14.25">
-      <c r="A38" s="5" t="s">
-        <v>19</v>
+      <c r="A38" s="2" t="s">
+        <v>18</v>
       </c>
       <c r="B38" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D38" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="14.25">
-      <c r="A39" s="2" t="s">
-        <v>20</v>
+      <c r="A39" s="5" t="s">
+        <v>19</v>
       </c>
       <c r="B39" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="D39" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="14.25">
-      <c r="A40" s="2" t="s">
-        <v>21</v>
+      <c r="A40" s="8" t="s">
+        <v>20</v>
       </c>
       <c r="B40" t="s">
         <v>24</v>
@@ -1211,10 +1249,13 @@
       <c r="D40" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="7" t="s">
-        <v>69</v>
+      <c r="E40" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" ht="14.25">
+      <c r="A41" s="8" t="s">
+        <v>21</v>
       </c>
       <c r="B41" t="s">
         <v>24</v>
@@ -1223,6 +1264,20 @@
         <v>46</v>
       </c>
       <c r="E41" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" ht="14.25">
+      <c r="A42" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="B42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" t="s">
+        <v>46</v>
+      </c>
+      <c r="E42" t="s">
         <v>48</v>
       </c>
     </row>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88F40C13-3569-4B41-A98E-9397D4FCD0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3B3DF2-403A-41A4-89A5-94DDF9D0F0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -92,9 +92,6 @@
     <t>riscv_core</t>
   </si>
   <si>
-    <t>riscv_tcm_top</t>
-  </si>
-  <si>
     <t>riscv_top</t>
   </si>
   <si>
@@ -249,13 +246,16 @@
   </si>
   <si>
     <t>dport_axi_fifo</t>
+  </si>
+  <si>
+    <t>riscv_tcm_top_multi</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -298,6 +298,11 @@
       <b/>
       <sz val="10"/>
       <color theme="1"/>
+      <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
@@ -350,7 +355,7 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -703,301 +708,301 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:9">
       <c r="A2" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
+        <v>31</v>
+      </c>
+      <c r="E2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" t="s">
-        <v>32</v>
-      </c>
-      <c r="E2" t="s">
-        <v>26</v>
-      </c>
       <c r="H2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="I2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="7" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>32</v>
+      </c>
+      <c r="E3" t="s">
+        <v>47</v>
+      </c>
+      <c r="H3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E3" t="s">
-        <v>48</v>
-      </c>
-      <c r="H3" t="s">
-        <v>28</v>
-      </c>
       <c r="I3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="7" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
         <v>29</v>
-      </c>
-      <c r="I4" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" s="7" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C5" t="s">
         <v>24</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" t="s">
         <v>25</v>
-      </c>
-      <c r="D5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E5" t="s">
-        <v>26</v>
       </c>
       <c r="F5" s="6"/>
       <c r="I5" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="7" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" s="7" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="D7" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E7" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="E8" t="s">
         <v>25</v>
-      </c>
-      <c r="E8" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="7" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" s="7" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D10" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E10" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="7" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
+        <v>23</v>
+      </c>
+      <c r="C11" t="s">
         <v>24</v>
       </c>
-      <c r="C11" t="s">
+      <c r="E11" t="s">
         <v>25</v>
-      </c>
-      <c r="E11" t="s">
-        <v>26</v>
       </c>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" s="7" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" s="7" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" s="7" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B14" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E14" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="7" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B15" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="7" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B17" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E18" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B19" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="7" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B20" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D20" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E20" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1005,10 +1010,10 @@
         <v>3</v>
       </c>
       <c r="B21" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D21" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.25">
@@ -1016,27 +1021,27 @@
         <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D22" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25">
       <c r="A23" s="8" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E23" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25">
@@ -1044,13 +1049,13 @@
         <v>5</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D24" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25">
@@ -1058,10 +1063,10 @@
         <v>6</v>
       </c>
       <c r="B25" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="26" spans="1:5" ht="14.25">
@@ -1069,10 +1074,10 @@
         <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="14.25">
@@ -1080,10 +1085,10 @@
         <v>8</v>
       </c>
       <c r="B27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D27" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="28" spans="1:5" ht="14.25">
@@ -1091,10 +1096,10 @@
         <v>9</v>
       </c>
       <c r="B28" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="1:5" ht="14.25">
@@ -1102,10 +1107,10 @@
         <v>10</v>
       </c>
       <c r="B29" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D29" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="1:5" ht="14.25">
@@ -1113,10 +1118,10 @@
         <v>11</v>
       </c>
       <c r="B30" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D30" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25">
@@ -1124,27 +1129,27 @@
         <v>12</v>
       </c>
       <c r="B31" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25">
       <c r="A32" s="8" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B32" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D32" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25">
@@ -1152,13 +1157,13 @@
         <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D33" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25">
@@ -1166,13 +1171,13 @@
         <v>14</v>
       </c>
       <c r="B34" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D34" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25">
@@ -1180,13 +1185,13 @@
         <v>15</v>
       </c>
       <c r="B35" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25">
@@ -1194,13 +1199,13 @@
         <v>16</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D36" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.25">
@@ -1208,81 +1213,82 @@
         <v>17</v>
       </c>
       <c r="B37" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D37" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="14.25">
-      <c r="A38" s="2" t="s">
-        <v>18</v>
+      <c r="A38" s="8" t="s">
+        <v>70</v>
       </c>
       <c r="B38" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D38" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="39" spans="1:5" ht="14.25">
       <c r="A39" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="D39" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:5" ht="14.25">
       <c r="A40" s="8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B40" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D40" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="41" spans="1:5" ht="14.25">
       <c r="A41" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B41" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D41" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="14.25">
       <c r="A42" s="9" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B42" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D42" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C3B3DF2-403A-41A4-89A5-94DDF9D0F0B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE6CFD5-B8F7-4F07-8F85-42758084743F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="72">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -249,6 +249,9 @@
   </si>
   <si>
     <t>riscv_tcm_top_multi</t>
+  </si>
+  <si>
+    <t>riscv_shared_mem_interconnect</t>
   </si>
 </sst>
 </file>
@@ -690,10 +693,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9373D2A7-8D80-423E-9070-95B67CA8F36B}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="26.875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" customWidth="1"/>
     <col min="4" max="4" width="17.875" customWidth="1"/>
     <col min="8" max="8" width="14.75" customWidth="1"/>
@@ -1286,6 +1289,17 @@
         <v>47</v>
       </c>
     </row>
+    <row r="43" spans="1:5" ht="14.25">
+      <c r="A43" s="9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B43" t="s">
+        <v>23</v>
+      </c>
+      <c r="E43" t="s">
+        <v>47</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BE6CFD5-B8F7-4F07-8F85-42758084743F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D871EB5-10E3-4CF5-8990-6F7AE58541FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="72">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -258,7 +258,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -289,13 +289,6 @@
       <family val="2"/>
       <charset val="177"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Arial Unicode MS"/>
-      <charset val="177"/>
     </font>
     <font>
       <b/>
@@ -347,18 +340,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,7 +713,7 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
         <v>48</v>
       </c>
       <c r="B2" t="s">
@@ -744,7 +736,7 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B3" t="s">
@@ -764,7 +756,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="6" t="s">
         <v>50</v>
       </c>
       <c r="B4" t="s">
@@ -784,7 +776,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="6" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
@@ -799,13 +791,13 @@
       <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="6"/>
+      <c r="F5" s="5"/>
       <c r="I5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="6" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
@@ -819,7 +811,7 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B7" t="s">
@@ -833,7 +825,7 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="6" t="s">
         <v>65</v>
       </c>
       <c r="B8" t="s">
@@ -847,7 +839,7 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="6" t="s">
         <v>66</v>
       </c>
       <c r="B9" t="s">
@@ -861,7 +853,7 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="6" t="s">
         <v>54</v>
       </c>
       <c r="B10" t="s">
@@ -875,7 +867,7 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="6" t="s">
         <v>55</v>
       </c>
       <c r="B11" t="s">
@@ -887,10 +879,10 @@
       <c r="E11" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="6"/>
+      <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="6" t="s">
         <v>56</v>
       </c>
       <c r="B12" t="s">
@@ -902,10 +894,10 @@
       <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="6"/>
+      <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B13" t="s">
@@ -919,7 +911,7 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="6" t="s">
         <v>58</v>
       </c>
       <c r="B14" t="s">
@@ -933,7 +925,7 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="6" t="s">
         <v>59</v>
       </c>
       <c r="B15" t="s">
@@ -956,10 +948,10 @@
       <c r="D16" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="6"/>
+      <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B17" t="s">
@@ -973,7 +965,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="7" t="s">
+      <c r="A18" s="6" t="s">
         <v>62</v>
       </c>
       <c r="B18" t="s">
@@ -995,7 +987,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="7" t="s">
+      <c r="A20" s="6" t="s">
         <v>64</v>
       </c>
       <c r="B20" t="s">
@@ -1020,7 +1012,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" ht="14.25">
-      <c r="A22" s="8" t="s">
+      <c r="A22" s="7" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
@@ -1034,7 +1026,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="7" t="s">
         <v>67</v>
       </c>
       <c r="B23" t="s">
@@ -1048,7 +1040,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25">
-      <c r="A24" s="8" t="s">
+      <c r="A24" s="7" t="s">
         <v>5</v>
       </c>
       <c r="B24" t="s">
@@ -1128,7 +1120,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" ht="14.25">
-      <c r="A31" s="8" t="s">
+      <c r="A31" s="7" t="s">
         <v>12</v>
       </c>
       <c r="B31" t="s">
@@ -1142,7 +1134,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25">
-      <c r="A32" s="8" t="s">
+      <c r="A32" s="7" t="s">
         <v>69</v>
       </c>
       <c r="B32" t="s">
@@ -1156,7 +1148,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25">
-      <c r="A33" s="8" t="s">
+      <c r="A33" s="7" t="s">
         <v>13</v>
       </c>
       <c r="B33" t="s">
@@ -1170,7 +1162,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25">
-      <c r="A34" s="8" t="s">
+      <c r="A34" s="7" t="s">
         <v>14</v>
       </c>
       <c r="B34" t="s">
@@ -1184,7 +1176,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25">
-      <c r="A35" s="8" t="s">
+      <c r="A35" s="7" t="s">
         <v>15</v>
       </c>
       <c r="B35" t="s">
@@ -1198,7 +1190,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25">
-      <c r="A36" s="8" t="s">
+      <c r="A36" s="7" t="s">
         <v>16</v>
       </c>
       <c r="B36" t="s">
@@ -1212,7 +1204,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.25">
-      <c r="A37" s="10" t="s">
+      <c r="A37" s="9" t="s">
         <v>17</v>
       </c>
       <c r="B37" t="s">
@@ -1226,7 +1218,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="14.25">
-      <c r="A38" s="8" t="s">
+      <c r="A38" s="7" t="s">
         <v>70</v>
       </c>
       <c r="B38" t="s">
@@ -1235,20 +1227,26 @@
       <c r="D38" t="s">
         <v>45</v>
       </c>
+      <c r="E38" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="39" spans="1:5" ht="14.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="9" t="s">
         <v>18</v>
       </c>
       <c r="B39" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="D39" t="s">
         <v>45</v>
       </c>
+      <c r="E39" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="40" spans="1:5" ht="14.25">
-      <c r="A40" s="8" t="s">
+      <c r="A40" s="7" t="s">
         <v>19</v>
       </c>
       <c r="B40" t="s">
@@ -1262,7 +1260,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="14.25">
-      <c r="A41" s="8" t="s">
+      <c r="A41" s="7" t="s">
         <v>20</v>
       </c>
       <c r="B41" t="s">
@@ -1276,7 +1274,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="14.25">
-      <c r="A42" s="9" t="s">
+      <c r="A42" s="8" t="s">
         <v>68</v>
       </c>
       <c r="B42" t="s">
@@ -1290,7 +1288,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" ht="14.25">
-      <c r="A43" s="9" t="s">
+      <c r="A43" s="8" t="s">
         <v>71</v>
       </c>
       <c r="B43" t="s">

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D871EB5-10E3-4CF5-8990-6F7AE58541FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9591CB6A-9A1B-4AAD-8EC7-136140044747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="76">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -252,6 +252,18 @@
   </si>
   <si>
     <t>riscv_shared_mem_interconnect</t>
+  </si>
+  <si>
+    <t>shared_memory_multi</t>
+  </si>
+  <si>
+    <t>coherence_defs</t>
+  </si>
+  <si>
+    <t>snoop_bus</t>
+  </si>
+  <si>
+    <t>coherence_controller</t>
   </si>
 </sst>
 </file>
@@ -302,18 +314,12 @@
       <name val="Arial Unicode MS"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -340,17 +346,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -685,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9373D2A7-8D80-423E-9070-95B67CA8F36B}">
-  <dimension ref="A1:I43"/>
+  <dimension ref="A1:I47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.875" style="1" bestFit="1" customWidth="1"/>
@@ -713,7 +717,7 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="4" t="s">
         <v>48</v>
       </c>
       <c r="B2" t="s">
@@ -736,7 +740,7 @@
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="4" t="s">
         <v>49</v>
       </c>
       <c r="B3" t="s">
@@ -756,7 +760,7 @@
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="4" t="s">
         <v>50</v>
       </c>
       <c r="B4" t="s">
@@ -776,7 +780,7 @@
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="4" t="s">
         <v>51</v>
       </c>
       <c r="B5" t="s">
@@ -791,13 +795,13 @@
       <c r="E5" t="s">
         <v>25</v>
       </c>
-      <c r="F5" s="5"/>
+      <c r="F5" s="3"/>
       <c r="I5" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="4" t="s">
         <v>52</v>
       </c>
       <c r="B6" t="s">
@@ -811,7 +815,7 @@
       </c>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="4" t="s">
         <v>53</v>
       </c>
       <c r="B7" t="s">
@@ -825,7 +829,7 @@
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="4" t="s">
         <v>65</v>
       </c>
       <c r="B8" t="s">
@@ -839,7 +843,7 @@
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="4" t="s">
         <v>66</v>
       </c>
       <c r="B9" t="s">
@@ -853,7 +857,7 @@
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="4" t="s">
         <v>54</v>
       </c>
       <c r="B10" t="s">
@@ -867,7 +871,7 @@
       </c>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="4" t="s">
         <v>55</v>
       </c>
       <c r="B11" t="s">
@@ -879,10 +883,10 @@
       <c r="E11" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="5"/>
+      <c r="F11" s="3"/>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
         <v>56</v>
       </c>
       <c r="B12" t="s">
@@ -894,10 +898,10 @@
       <c r="E12" t="s">
         <v>47</v>
       </c>
-      <c r="F12" s="5"/>
+      <c r="F12" s="3"/>
     </row>
     <row r="13" spans="1:9">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="4" t="s">
         <v>57</v>
       </c>
       <c r="B13" t="s">
@@ -911,7 +915,7 @@
       </c>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="4" t="s">
         <v>58</v>
       </c>
       <c r="B14" t="s">
@@ -925,7 +929,7 @@
       </c>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="4" t="s">
         <v>59</v>
       </c>
       <c r="B15" t="s">
@@ -945,19 +949,19 @@
       <c r="B16" t="s">
         <v>26</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F16" s="5"/>
+      <c r="F16" s="3"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="A17" s="4" t="s">
         <v>61</v>
       </c>
       <c r="B17" t="s">
         <v>26</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="E17" t="s">
@@ -965,7 +969,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="A18" s="4" t="s">
         <v>62</v>
       </c>
       <c r="B18" t="s">
@@ -979,15 +983,18 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="4" t="s">
         <v>63</v>
       </c>
       <c r="B19" t="s">
         <v>23</v>
       </c>
+      <c r="E19" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="A20" s="4" t="s">
         <v>64</v>
       </c>
       <c r="B20" t="s">
@@ -1001,7 +1008,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="1" t="s">
+      <c r="A21" s="4" t="s">
         <v>3</v>
       </c>
       <c r="B21" t="s">
@@ -1010,9 +1017,12 @@
       <c r="D21" t="s">
         <v>43</v>
       </c>
+      <c r="E21" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="22" spans="1:5" ht="14.25">
-      <c r="A22" s="7" t="s">
+      <c r="A22" s="5" t="s">
         <v>4</v>
       </c>
       <c r="B22" t="s">
@@ -1026,7 +1036,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="14.25">
-      <c r="A23" s="7" t="s">
+      <c r="A23" s="5" t="s">
         <v>67</v>
       </c>
       <c r="B23" t="s">
@@ -1040,7 +1050,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" ht="14.25">
-      <c r="A24" s="7" t="s">
+      <c r="A24" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B24" t="s">
@@ -1054,7 +1064,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" ht="14.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B25" t="s">
@@ -1063,9 +1073,12 @@
       <c r="D25" t="s">
         <v>29</v>
       </c>
+      <c r="E25" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="26" spans="1:5" ht="14.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" s="5" t="s">
         <v>7</v>
       </c>
       <c r="B26" t="s">
@@ -1074,9 +1087,12 @@
       <c r="D26" t="s">
         <v>44</v>
       </c>
+      <c r="E26" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="27" spans="1:5" ht="14.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B27" t="s">
@@ -1085,9 +1101,12 @@
       <c r="D27" t="s">
         <v>44</v>
       </c>
+      <c r="E27" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="28" spans="1:5" ht="14.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" s="5" t="s">
         <v>9</v>
       </c>
       <c r="B28" t="s">
@@ -1096,9 +1115,12 @@
       <c r="D28" t="s">
         <v>44</v>
       </c>
+      <c r="E28" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="29" spans="1:5" ht="14.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B29" t="s">
@@ -1107,9 +1129,12 @@
       <c r="D29" t="s">
         <v>44</v>
       </c>
+      <c r="E29" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="30" spans="1:5" ht="14.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" s="5" t="s">
         <v>11</v>
       </c>
       <c r="B30" t="s">
@@ -1118,9 +1143,12 @@
       <c r="D30" t="s">
         <v>44</v>
       </c>
+      <c r="E30" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="31" spans="1:5" ht="14.25">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B31" t="s">
@@ -1134,7 +1162,7 @@
       </c>
     </row>
     <row r="32" spans="1:5" ht="14.25">
-      <c r="A32" s="7" t="s">
+      <c r="A32" s="5" t="s">
         <v>69</v>
       </c>
       <c r="B32" t="s">
@@ -1148,7 +1176,7 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="14.25">
-      <c r="A33" s="7" t="s">
+      <c r="A33" s="5" t="s">
         <v>13</v>
       </c>
       <c r="B33" t="s">
@@ -1162,7 +1190,7 @@
       </c>
     </row>
     <row r="34" spans="1:5" ht="14.25">
-      <c r="A34" s="7" t="s">
+      <c r="A34" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B34" t="s">
@@ -1176,7 +1204,7 @@
       </c>
     </row>
     <row r="35" spans="1:5" ht="14.25">
-      <c r="A35" s="7" t="s">
+      <c r="A35" s="5" t="s">
         <v>15</v>
       </c>
       <c r="B35" t="s">
@@ -1190,7 +1218,7 @@
       </c>
     </row>
     <row r="36" spans="1:5" ht="14.25">
-      <c r="A36" s="7" t="s">
+      <c r="A36" s="5" t="s">
         <v>16</v>
       </c>
       <c r="B36" t="s">
@@ -1204,7 +1232,7 @@
       </c>
     </row>
     <row r="37" spans="1:5" ht="14.25">
-      <c r="A37" s="9" t="s">
+      <c r="A37" s="7" t="s">
         <v>17</v>
       </c>
       <c r="B37" t="s">
@@ -1218,7 +1246,7 @@
       </c>
     </row>
     <row r="38" spans="1:5" ht="14.25">
-      <c r="A38" s="7" t="s">
+      <c r="A38" s="5" t="s">
         <v>70</v>
       </c>
       <c r="B38" t="s">
@@ -1232,7 +1260,7 @@
       </c>
     </row>
     <row r="39" spans="1:5" ht="14.25">
-      <c r="A39" s="9" t="s">
+      <c r="A39" s="7" t="s">
         <v>18</v>
       </c>
       <c r="B39" t="s">
@@ -1246,7 +1274,7 @@
       </c>
     </row>
     <row r="40" spans="1:5" ht="14.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B40" t="s">
@@ -1260,7 +1288,7 @@
       </c>
     </row>
     <row r="41" spans="1:5" ht="14.25">
-      <c r="A41" s="7" t="s">
+      <c r="A41" s="5" t="s">
         <v>20</v>
       </c>
       <c r="B41" t="s">
@@ -1274,7 +1302,7 @@
       </c>
     </row>
     <row r="42" spans="1:5" ht="14.25">
-      <c r="A42" s="8" t="s">
+      <c r="A42" s="6" t="s">
         <v>68</v>
       </c>
       <c r="B42" t="s">
@@ -1288,13 +1316,57 @@
       </c>
     </row>
     <row r="43" spans="1:5" ht="14.25">
-      <c r="A43" s="8" t="s">
+      <c r="A43" s="6" t="s">
         <v>71</v>
       </c>
       <c r="B43" t="s">
         <v>23</v>
       </c>
       <c r="E43" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" ht="14.25">
+      <c r="A44" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B44" t="s">
+        <v>23</v>
+      </c>
+      <c r="E44" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" ht="14.25">
+      <c r="A45" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" t="s">
+        <v>23</v>
+      </c>
+      <c r="E45" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="14.25">
+      <c r="A46" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B46" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" ht="14.25">
+      <c r="A47" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="B47" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" t="s">
         <v>47</v>
       </c>
     </row>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9591CB6A-9A1B-4AAD-8EC7-136140044747}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC7A897-BE16-446F-B659-3BF63B355C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="77">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -264,6 +264,9 @@
   </si>
   <si>
     <t>coherence_controller</t>
+  </si>
+  <si>
+    <t>finiah</t>
   </si>
 </sst>
 </file>
@@ -943,7 +946,7 @@
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="4" t="s">
         <v>60</v>
       </c>
       <c r="B16" t="s">
@@ -951,6 +954,9 @@
       </c>
       <c r="D16" s="2" t="s">
         <v>41</v>
+      </c>
+      <c r="E16" t="s">
+        <v>76</v>
       </c>
       <c r="F16" s="3"/>
     </row>

--- a/component_end_dates.xlsx
+++ b/component_end_dates.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\97250\Documents\CoreStorm_git\CoreStorm_RV32I\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4EC7A897-BE16-446F-B659-3BF63B355C7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{11DD654E-BA1B-4A10-BD4C-42E21F2B9FC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{58139526-2888-40EA-BA21-B55B9EAF3B56}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="83">
   <si>
     <t>Task_moudel</t>
   </si>
@@ -267,13 +267,31 @@
   </si>
   <si>
     <t>finiah</t>
+  </si>
+  <si>
+    <t>dcache_core_l2</t>
+  </si>
+  <si>
+    <t>l2_arbiter</t>
+  </si>
+  <si>
+    <t>l2_data_ram</t>
+  </si>
+  <si>
+    <t>l2_tag_ram</t>
+  </si>
+  <si>
+    <t>shared_l2_cachce_multi</t>
+  </si>
+  <si>
+    <t>shared_l2_cachce_single</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -316,6 +334,12 @@
       <sz val="10"/>
       <name val="Arial Unicode MS"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial Unicode MS"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -349,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -358,6 +382,7 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -692,7 +717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9373D2A7-8D80-423E-9070-95B67CA8F36B}">
-  <dimension ref="A1:I47"/>
+  <dimension ref="A1:I53"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="26.875" style="1" bestFit="1" customWidth="1"/>
@@ -1322,7 +1347,7 @@
       </c>
     </row>
     <row r="43" spans="1:5" ht="14.25">
-      <c r="A43" s="6" t="s">
+      <c r="A43" s="8" t="s">
         <v>71</v>
       </c>
       <c r="B43" t="s">
@@ -1333,7 +1358,7 @@
       </c>
     </row>
     <row r="44" spans="1:5" ht="14.25">
-      <c r="A44" s="6" t="s">
+      <c r="A44" s="8" t="s">
         <v>72</v>
       </c>
       <c r="B44" t="s">
@@ -1355,7 +1380,7 @@
       </c>
     </row>
     <row r="46" spans="1:5" ht="14.25">
-      <c r="A46" s="6" t="s">
+      <c r="A46" s="8" t="s">
         <v>74</v>
       </c>
       <c r="B46" t="s">
@@ -1374,6 +1399,36 @@
       </c>
       <c r="E47" t="s">
         <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" ht="14.25">
+      <c r="A48" s="5" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1" ht="14.25">
+      <c r="A49" s="5" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1" ht="14.25">
+      <c r="A50" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1" ht="14.25">
+      <c r="A51" s="5" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1" ht="14.25">
+      <c r="A52" s="5" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1" ht="14.25">
+      <c r="A53" s="5" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>
